--- a/TIMES-NZ/v303/SuppXLS/Demands/ScenDem_Transformation.xlsx
+++ b/TIMES-NZ/v303/SuppXLS/Demands/ScenDem_Transformation.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AllRegions</t>
+          <t>AGR_ADCF_DMD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -662,187 +662,187 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>0.9706</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.998001</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.997002999</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.996005996001</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.995009990004999</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.994014980014994</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.993020965034979</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.992027944069944</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.9910359161258742</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.9900448802097482</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.9890548353295384</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.988065780494209</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.9870777147137147</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.986090636999001</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.985104546362002</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.98411944181564</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.9831353223738244</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.9821521870514506</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.9811700348643992</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.9801888648295348</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.9792086759647052</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.9782294672887404</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.9772512378214516</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.9762739865836304</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.9752977125970468</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.9743224148844496</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AGR_ADCF_DMD</t>
+          <t>AGR_AFISH_DMD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -864,187 +864,187 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.9706</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AGR_AFISH_DMD</t>
+          <t>AGR_AFORE_DMD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1066,187 +1066,187 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0238</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0476</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0666600000000002</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.08572</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.10478</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.12384</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1429</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.15242</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.16194</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.17146</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.18098</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1905</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2095399999999998</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.22858</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.24762</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.26666</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2857</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.30476</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.32382</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.34288</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.36194</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.381</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.40004</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.41908</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.43812</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.45716</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AGR_AFORE_DMD</t>
+          <t>AGR_AHORT_DMD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1268,187 +1268,187 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.0238</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.0476</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.0666600000000002</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.08572</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.10478</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.12384</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.1429</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.15242</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.16194</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1.17146</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.18098</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.1905</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.2095399999999998</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.22858</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.24762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1.26666</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.2857</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.30476</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>1.32382</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.34288</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1.36194</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1.381</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.40004</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.41908</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>1.43812</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1.45716</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AGR_AHORT_DMD</t>
+          <t>AGR_AINDC_DMD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AGR_AINDC_DMD</t>
+          <t>AGR_ALIVE_DMD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1672,187 +1672,187 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.98665</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9733</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.96798</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.96266</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.95734</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.95202</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9467</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9387</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9307</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9227</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9147</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9067</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.90136</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8960199999999999</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.89068</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.88534</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.872</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.864</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.856</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.848</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.83466</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.82932</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.82398</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.81864</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AGR_ALIVE_DMD</t>
+          <t>AGR_AOTH_DMD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1874,187 +1874,187 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.98665</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.9733</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.96798</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.96266</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.95734</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.95202</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.9467</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.9387</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.9307</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.9227</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.9147</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.9067</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.90136</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.8960199999999999</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.89068</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.88534</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.872</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.83466</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.82932</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.82398</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.81864</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AGR_AOTH_DMD</t>
+          <t>COM_DATA_DMD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2076,187 +2076,187 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.5816326530612246</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.163265306122449</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.7448979591836733</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.326530612244898</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.9081632653061225</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.489795918367347</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.071428571428571</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.482352941176471</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.893277310924369</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.30420168067227</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.715126050420167</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>COM_DATA_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2278,187 +2278,187 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.5816326530612246</t>
+          <t>1.0303408071425741</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.163265306122449</t>
+          <t>1.0572299466396682</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2.7448979591836733</t>
+          <t>1.0887183071695965</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3.326530612244898</t>
+          <t>1.1181802865820922</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.9081632653061225</t>
+          <t>1.1456520769455265</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.489795918367347</t>
+          <t>1.1720275737082368</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.071428571428571</t>
+          <t>1.1960494078480401</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6.482352941176471</t>
+          <t>1.2174367476499477</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>7.893277310924369</t>
+          <t>1.2379125877779258</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>9.30420168067227</t>
+          <t>1.2578882099248054</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>10.715126050420167</t>
+          <t>1.2773421222351529</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.2962296079582918</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.3145929986632894</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.332729959250145</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.35086007054661</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.3689955791271387</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.3870949713021579</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.4050402526418948</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.4227561926448493</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.4402392351565683</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.457509805546448</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.474542909849503</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.4912784717543335</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.5076572652559745</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.5236723870191355</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.539308470277106</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>IND_ALUM_DMD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2480,187 +2480,187 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.0303408071425741</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.0572299466396682</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.0887183071695965</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.1181802865820922</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.1456520769455265</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.1720275737082368</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.1960494078480401</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.2174367476499477</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.2379125877779258</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1.2578882099248054</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1.2773421222351529</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.2962296079582918</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1.3145929986632894</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.332729959250145</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.35086007054661</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1.3689955791271387</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1.3870949713021579</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1.4050402526418948</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1.4227561926448493</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>1.4402392351565683</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>1.457509805546448</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1.474542909849503</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.4912784717543335</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.5076572652559745</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>1.5236723870191355</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>1.539308470277106</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IND_ALUM_DMD</t>
+          <t>IND_CHEM_DMD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IND_CHEM_DMD</t>
+          <t>IND_CNST_DMD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2884,187 +2884,187 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.019</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.038361</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.058089859</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0781935663209998</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0986792440810986</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1195541497186394</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1408256785632935</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.162501366455996</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1845888924186598</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2070960813746143</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2300309069207318</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2534014941522256</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2772161225411178</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.301483228869399</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.3262114102179174</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.3514094270120578</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.3770862061252869</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4032508440416671</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4299126100784587</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4570809496699493</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4847654877136782</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.512976031980238</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.5417225765878622</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.5710153055430314</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6008645963483488</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6312810236789672</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IND_CNST_DMD</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3086,187 +3086,187 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.019</t>
+          <t>1.028</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.038361</t>
+          <t>1.0452704</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.058089859</t>
+          <t>1.05112391424</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.0781935663209998</t>
+          <t>1.0452376203202558</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.0986792440810986</t>
+          <t>1.0276776282988755</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.1195541497186394</t>
+          <t>0.998902654706507</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.1408256785632935</t>
+          <t>0.9709333803747248</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.162501366455996</t>
+          <t>0.9437472457242324</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.1845888924186598</t>
+          <t>0.917322322843954</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1.2070960813746143</t>
+          <t>0.8916372978043231</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1.2300309069207318</t>
+          <t>0.866671453465802</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.2534014941522256</t>
+          <t>0.8424046527687595</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1.2772161225411178</t>
+          <t>0.8188173224912343</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.301483228869399</t>
+          <t>0.7958904374614797</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.3262114102179174</t>
+          <t>0.7736055052125582</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1.3514094270120578</t>
+          <t>0.7519445510666066</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.3770862061252869</t>
+          <t>0.7308901036367417</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1.4032508440416671</t>
+          <t>0.7104251807349129</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1.4299126100784587</t>
+          <t>0.6905332756743353</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1.4570809496699493</t>
+          <t>0.6711983439554539</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>1.4847654877136782</t>
+          <t>0.6524047903247011</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>1.512976031980238</t>
+          <t>0.6341374561956095</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.5417225765878622</t>
+          <t>0.6163816074221323</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.5710153055430314</t>
+          <t>0.5991229224143126</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>1.6008645963483488</t>
+          <t>0.5823474805867118</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>1.6312810236789672</t>
+          <t>0.5660417511302839</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>IND_FOOD_DMD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3288,187 +3288,187 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.028</t>
+          <t>0.983</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.0452704</t>
+          <t>0.9729734</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.05112391424</t>
+          <t>0.96966529044</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.0452376203202558</t>
+          <t>0.972962152427496</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.0276776282988755</t>
+          <t>0.9828863663822563</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.998902654706507</t>
+          <t>0.9995954346107548</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.9709333803747248</t>
+          <t>1.0165885569991375</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.9437472457242324</t>
+          <t>1.0338705624681228</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.917322322843954</t>
+          <t>1.051446362030081</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.8916372978043231</t>
+          <t>1.0693209501845922</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.866671453465802</t>
+          <t>1.08749940633773</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.8424046527687595</t>
+          <t>1.1059868962454715</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.8188173224912343</t>
+          <t>1.1247886734816444</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.7958904374614797</t>
+          <t>1.1439100809308322</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.7736055052125582</t>
+          <t>1.1633565523066562</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.7519445510666066</t>
+          <t>1.1831336136958692</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.7308901036367417</t>
+          <t>1.2032468851286988</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.7104251807349129</t>
+          <t>1.2237020821758866</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.6905332756743353</t>
+          <t>1.2445050175728765</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.6711983439554539</t>
+          <t>1.2656616028716152</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>0.6524047903247011</t>
+          <t>1.2871778501204325</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>0.6341374561956095</t>
+          <t>1.3090598735724797</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.6163816074221323</t>
+          <t>1.3313138914232117</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.5991229224143126</t>
+          <t>1.353946227577406</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.5823474805867118</t>
+          <t>1.3769633134462218</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>0.5660417511302839</t>
+          <t>1.4003716897748075</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>IND_MEAT_DMD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3490,187 +3490,187 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>1.007</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.9729734</t>
+          <t>1.0112294</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.96966529044</t>
+          <t>1.01264512116</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.972962152427496</t>
+          <t>1.0112274179903762</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.9828863663822563</t>
+          <t>1.0069802628348166</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.9995954346107548</t>
+          <t>0.9999314009949728</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.0165885569991375</t>
+          <t>0.992931881188008</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.0338705624681228</t>
+          <t>0.985981358019692</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.051446362030081</t>
+          <t>0.9790794885135542</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1.0693209501845922</t>
+          <t>0.9722259320939594</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1.08749940633773</t>
+          <t>0.9654203505693016</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>1.1059868962454715</t>
+          <t>0.9586624081153166</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1.1247886734816444</t>
+          <t>0.9519517712585094</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.1439100809308322</t>
+          <t>0.9452881088596998</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.1633565523066562</t>
+          <t>0.938671092097682</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1.1831336136958692</t>
+          <t>0.9321003944529982</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1.2032468851286988</t>
+          <t>0.9255756916918272</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1.2237020821758866</t>
+          <t>0.9190966618499844</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>1.2445050175728765</t>
+          <t>0.9126629852170344</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>1.2656616028716152</t>
+          <t>0.9062743443205152</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>1.2871778501204325</t>
+          <t>0.8999304239102717</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>1.3090598735724797</t>
+          <t>0.8936309109428998</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.3313138914232117</t>
+          <t>0.8873754945662995</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.353946227577406</t>
+          <t>0.8811638661043354</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>1.3769633134462218</t>
+          <t>0.874995719041605</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>1.4003716897748075</t>
+          <t>0.8688707490083137</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IND_MEAT_DMD</t>
+          <t>IND_METH_DMD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3692,187 +3692,187 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.007</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.0112294</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.01264512116</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.0112274179903762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.0069802628348166</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.9999314009949728</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.992931881188008</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.985981358019692</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.9790794885135542</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.9722259320939594</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.9654203505693016</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.9586624081153166</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.9519517712585094</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.9452881088596998</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.938671092097682</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.9321003944529982</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.9255756916918272</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.9190966618499844</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.9126629852170344</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.9062743443205152</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>0.8999304239102717</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>0.8936309109428998</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.8873754945662995</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.8811638661043354</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.874995719041605</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>0.8688707490083137</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IND_METH_DMD</t>
+          <t>IND_MINE_DMD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3894,187 +3894,187 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.012</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0217152</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0290715494400002</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.034011092877312</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IND_MINE_DMD</t>
+          <t>IND_MNRL_DMD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4096,187 +4096,187 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.012</t>
+          <t>0.954</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.0217152</t>
+          <t>0.910116</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.0290715494400002</t>
+          <t>0.8682506639999998</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.034011092877312</t>
+          <t>0.8283111334559998</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.7902088213170237</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.7538592155364406</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.7191816916217644</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.6860993338071631</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.6545387644520336</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.62442998128724</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.5957062021480269</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.5683037168492177</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.5421617458741537</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.5172223055639426</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.4934300795080011</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.4707322958506331</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.449078610241504</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.4284209941703947</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.4087136284385566</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.3899128015303829</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.3719768126599853</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.3548658792776259</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.3385420488308551</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.3229691145846357</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.3081125353137425</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.2939393586893103</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IND_MNRL_DMD</t>
+          <t>IND_OTHR_DMD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4298,187 +4298,187 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.954</t>
+          <t>0.999</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.910116</t>
+          <t>0.998001</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.8682506639999998</t>
+          <t>0.997002999</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.8283111334559998</t>
+          <t>0.996005996001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.7902088213170237</t>
+          <t>0.995009990004999</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.7538592155364406</t>
+          <t>0.994014980014994</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.7191816916217644</t>
+          <t>0.993020965034979</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.6860993338071631</t>
+          <t>0.992027944069944</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.6545387644520336</t>
+          <t>0.9910359161258742</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.62442998128724</t>
+          <t>0.9900448802097482</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.5957062021480269</t>
+          <t>0.9890548353295384</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.5683037168492177</t>
+          <t>0.988065780494209</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.5421617458741537</t>
+          <t>0.9870777147137147</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.5172223055639426</t>
+          <t>0.986090636999001</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.4934300795080011</t>
+          <t>0.985104546362002</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.4707322958506331</t>
+          <t>0.98411944181564</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.449078610241504</t>
+          <t>0.9831353223738244</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.4284209941703947</t>
+          <t>0.9821521870514506</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.4087136284385566</t>
+          <t>0.9811700348643992</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.3899128015303829</t>
+          <t>0.9801888648295348</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>0.3719768126599853</t>
+          <t>0.9792086759647052</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>0.3548658792776259</t>
+          <t>0.9782294672887404</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.3385420488308551</t>
+          <t>0.9772512378214516</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.3229691145846357</t>
+          <t>0.9762739865836304</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.3081125353137425</t>
+          <t>0.9752977125970468</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>0.2939393586893103</t>
+          <t>0.9743224148844496</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AllRegions</t>
+          <t>AGR_ADCF_DMD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6924,187 +6924,187 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>0.9706</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.998001</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.997002999</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.996005996001</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.995009990004999</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.994014980014994</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.993020965034979</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.992027944069944</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.9910359161258742</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.9900448802097482</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.9890548353295384</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.988065780494209</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.9870777147137147</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.986090636999001</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.985104546362002</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.98411944181564</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.9831353223738244</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.9821521870514506</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.9811700348643992</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>0.9801888648295348</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>0.9792086759647052</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>0.9782294672887404</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>0.9772512378214516</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>0.9762739865836304</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>0.9752977125970468</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>0.9743224148844496</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>0.9733480924695652</t>
+          <t>0.9412</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AGR_ADCF_DMD</t>
+          <t>AGR_AFISH_DMD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -7126,187 +7126,187 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.9706</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>0.9412</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -7318,7 +7318,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AGR_AFISH_DMD</t>
+          <t>AGR_AFORE_DMD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -7328,187 +7328,187 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0238</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0476</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0666600000000002</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.08572</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.10478</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.12384</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1429</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.15242</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.16194</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.17146</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.18098</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1905</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2095399999999998</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.22858</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.24762</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.26666</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2857</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.30476</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.32382</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.34288</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.36194</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.381</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.40004</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.41908</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.43812</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.45716</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4762</t>
         </is>
       </c>
     </row>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AGR_AFORE_DMD</t>
+          <t>AGR_AHORT_DMD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -7530,187 +7530,187 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.0238</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.0476</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.0666600000000002</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.08572</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.10478</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.12384</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1.1429</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.15242</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1.16194</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1.17146</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>1.18098</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>1.1905</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>1.2095399999999998</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1.22858</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1.24762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1.26666</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1.2857</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>1.30476</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>1.32382</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>1.34288</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>1.36194</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>1.381</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>1.40004</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>1.41908</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>1.43812</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>1.45716</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>1.4762</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AGR_AHORT_DMD</t>
+          <t>AGR_AINDC_DMD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AGR_AINDC_DMD</t>
+          <t>AGR_ALIVE_DMD</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -7934,187 +7934,187 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.98665</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9733</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.96798</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.96266</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.95734</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.95202</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9467</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9387</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9307</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9227</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9147</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9067</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.90136</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8960199999999999</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.89068</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.88534</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.872</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.864</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.856</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.848</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.83466</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.82932</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.82398</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.81864</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8133</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AGR_ALIVE_DMD</t>
+          <t>AGR_AOTH_DMD</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -8136,187 +8136,187 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.98665</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.9733</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.96798</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.96266</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.95734</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.95202</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.9467</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.9387</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.9307</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.9227</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.9147</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.9067</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.90136</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.8960199999999999</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>0.89068</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>0.88534</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0.872</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>0.83466</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>0.82932</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>0.82398</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>0.81864</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>0.8133</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AGR_AOTH_DMD</t>
+          <t>COM_DATA_DMD</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -8338,187 +8338,187 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.5816326530612246</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.163265306122449</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.7448979591836733</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.326530612244898</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.9081632653061225</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.489795918367347</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.071428571428571</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.482352941176471</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.893277310924369</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.30420168067227</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.715126050420167</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.126050420168069</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>COM_DATA_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -8540,187 +8540,187 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.5816326530612246</t>
+          <t>1.0303408071425741</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2.163265306122449</t>
+          <t>1.0572299466396682</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2.7448979591836733</t>
+          <t>1.0887183071695965</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3.326530612244898</t>
+          <t>1.1181802865820922</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.9081632653061225</t>
+          <t>1.1456520769455265</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4.489795918367347</t>
+          <t>1.1720275737082368</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>5.071428571428571</t>
+          <t>1.1960494078480401</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>6.482352941176471</t>
+          <t>1.2174367476499477</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>7.893277310924369</t>
+          <t>1.2379125877779258</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>9.30420168067227</t>
+          <t>1.2578882099248054</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>10.715126050420167</t>
+          <t>1.2773421222351529</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.2962296079582918</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.3145929986632894</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.332729959250145</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.35086007054661</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.3689955791271387</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.3870949713021579</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.4050402526418948</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.4227561926448493</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.4402392351565683</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.457509805546448</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.474542909849503</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.4912784717543335</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.5076572652559745</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.5236723870191355</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.539308470277106</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>12.126050420168069</t>
+          <t>1.55448066813909</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>IND_ALUM_DMD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -8742,187 +8742,187 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.0303408071425741</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.0572299466396682</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.0887183071695965</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.1181802865820922</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1.1456520769455265</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1.1720275737082368</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>1.1960494078480401</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1.2174367476499477</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1.2379125877779258</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1.2578882099248054</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1.2773421222351529</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>1.2962296079582918</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1.3145929986632894</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1.332729959250145</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1.35086007054661</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1.3689955791271387</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1.3870949713021579</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>1.4050402526418948</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>1.4227561926448493</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>1.4402392351565683</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>1.457509805546448</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>1.474542909849503</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>1.4912784717543335</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>1.5076572652559745</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>1.5236723870191355</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>1.539308470277106</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>1.55448066813909</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IND_ALUM_DMD</t>
+          <t>IND_CHEM_DMD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IND_CHEM_DMD</t>
+          <t>IND_CNST_DMD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -9146,187 +9146,187 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.019</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.038361</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.058089859</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0781935663209998</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0986792440810986</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1195541497186394</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1408256785632935</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.162501366455996</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1845888924186598</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2070960813746143</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2300309069207318</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2534014941522256</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2772161225411178</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.301483228869399</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.3262114102179174</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.3514094270120578</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.3770862061252869</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4032508440416671</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4299126100784587</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4570809496699493</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4847654877136782</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.512976031980238</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.5417225765878622</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.5710153055430314</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6008645963483488</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6312810236789672</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6622753631288674</t>
         </is>
       </c>
     </row>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IND_CNST_DMD</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -9348,187 +9348,187 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.019</t>
+          <t>1.028</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.038361</t>
+          <t>1.0452704</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.058089859</t>
+          <t>1.05112391424</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.0781935663209998</t>
+          <t>1.0452376203202558</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.0986792440810986</t>
+          <t>1.0276776282988755</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.1195541497186394</t>
+          <t>0.998902654706507</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1.1408256785632935</t>
+          <t>0.9709333803747248</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1.162501366455996</t>
+          <t>0.9437472457242324</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1.1845888924186598</t>
+          <t>0.917322322843954</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1.2070960813746143</t>
+          <t>0.8916372978043231</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1.2300309069207318</t>
+          <t>0.866671453465802</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>1.2534014941522256</t>
+          <t>0.8424046527687595</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>1.2772161225411178</t>
+          <t>0.8188173224912343</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>1.301483228869399</t>
+          <t>0.7958904374614797</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1.3262114102179174</t>
+          <t>0.7736055052125582</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1.3514094270120578</t>
+          <t>0.7519445510666066</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1.3770862061252869</t>
+          <t>0.7308901036367417</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>1.4032508440416671</t>
+          <t>0.7104251807349129</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>1.4299126100784587</t>
+          <t>0.6905332756743353</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>1.4570809496699493</t>
+          <t>0.6711983439554539</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>1.4847654877136782</t>
+          <t>0.6524047903247011</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>1.512976031980238</t>
+          <t>0.6341374561956095</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>1.5417225765878622</t>
+          <t>0.6163816074221323</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>1.5710153055430314</t>
+          <t>0.5991229224143126</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>1.6008645963483488</t>
+          <t>0.5823474805867118</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>1.6312810236789672</t>
+          <t>0.5660417511302839</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>1.6622753631288674</t>
+          <t>0.5501925820986359</t>
         </is>
       </c>
     </row>
@@ -9540,7 +9540,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>IND_FOOD_DMD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -9550,187 +9550,187 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.028</t>
+          <t>0.983</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.0452704</t>
+          <t>0.9729734</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.05112391424</t>
+          <t>0.96966529044</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.0452376203202558</t>
+          <t>0.972962152427496</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1.0276776282988755</t>
+          <t>0.9828863663822563</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.998902654706507</t>
+          <t>0.9995954346107548</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.9709333803747248</t>
+          <t>1.0165885569991375</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>0.9437472457242324</t>
+          <t>1.0338705624681228</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0.917322322843954</t>
+          <t>1.051446362030081</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>0.8916372978043231</t>
+          <t>1.0693209501845922</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>0.866671453465802</t>
+          <t>1.08749940633773</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>0.8424046527687595</t>
+          <t>1.1059868962454715</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>0.8188173224912343</t>
+          <t>1.1247886734816444</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>0.7958904374614797</t>
+          <t>1.1439100809308322</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>0.7736055052125582</t>
+          <t>1.1633565523066562</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>0.7519445510666066</t>
+          <t>1.1831336136958692</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>0.7308901036367417</t>
+          <t>1.2032468851286988</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>0.7104251807349129</t>
+          <t>1.2237020821758866</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>0.6905332756743353</t>
+          <t>1.2445050175728765</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>0.6711983439554539</t>
+          <t>1.2656616028716152</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>0.6524047903247011</t>
+          <t>1.2871778501204325</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>0.6341374561956095</t>
+          <t>1.3090598735724797</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>0.6163816074221323</t>
+          <t>1.3313138914232117</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>0.5991229224143126</t>
+          <t>1.353946227577406</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>0.5823474805867118</t>
+          <t>1.3769633134462218</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>0.5660417511302839</t>
+          <t>1.4003716897748075</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>0.5501925820986359</t>
+          <t>1.4241780085009792</t>
         </is>
       </c>
     </row>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>IND_MEAT_DMD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -9752,187 +9752,187 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>1.007</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.9729734</t>
+          <t>1.0112294</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.96966529044</t>
+          <t>1.01264512116</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.972962152427496</t>
+          <t>1.0112274179903762</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.9828863663822563</t>
+          <t>1.0069802628348166</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.9995954346107548</t>
+          <t>0.9999314009949728</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1.0165885569991375</t>
+          <t>0.992931881188008</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1.0338705624681228</t>
+          <t>0.985981358019692</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1.051446362030081</t>
+          <t>0.9790794885135542</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1.0693209501845922</t>
+          <t>0.9722259320939594</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1.08749940633773</t>
+          <t>0.9654203505693016</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>1.1059868962454715</t>
+          <t>0.9586624081153166</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>1.1247886734816444</t>
+          <t>0.9519517712585094</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>1.1439100809308322</t>
+          <t>0.9452881088596998</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1.1633565523066562</t>
+          <t>0.938671092097682</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1.1831336136958692</t>
+          <t>0.9321003944529982</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1.2032468851286988</t>
+          <t>0.9255756916918272</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>1.2237020821758866</t>
+          <t>0.9190966618499844</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>1.2445050175728765</t>
+          <t>0.9126629852170344</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>1.2656616028716152</t>
+          <t>0.9062743443205152</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>1.2871778501204325</t>
+          <t>0.8999304239102717</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>1.3090598735724797</t>
+          <t>0.8936309109428998</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>1.3313138914232117</t>
+          <t>0.8873754945662995</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>1.353946227577406</t>
+          <t>0.8811638661043354</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>1.3769633134462218</t>
+          <t>0.874995719041605</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>1.4003716897748075</t>
+          <t>0.8688707490083137</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>1.4241780085009792</t>
+          <t>0.8627886537652555</t>
         </is>
       </c>
     </row>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IND_MEAT_DMD</t>
+          <t>IND_METH_DMD</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -9954,187 +9954,187 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.007</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.0112294</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.01264512116</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.0112274179903762</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1.0069802628348166</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.9999314009949728</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.992931881188008</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.985981358019692</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.9790794885135542</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0.9722259320939594</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0.9654203505693016</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.9586624081153166</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>0.9519517712585094</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>0.9452881088596998</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0.938671092097682</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>0.9321003944529982</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>0.9255756916918272</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>0.9190966618499844</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>0.9126629852170344</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>0.9062743443205152</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>0.8999304239102717</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>0.8936309109428998</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>0.8873754945662995</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>0.8811638661043354</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>0.874995719041605</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>0.8688707490083137</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>0.8627886537652555</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IND_METH_DMD</t>
+          <t>IND_MINE_DMD</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -10156,187 +10156,187 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.012</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0217152</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0290715494400002</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.034011092877312</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0364927195002176</t>
         </is>
       </c>
     </row>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IND_MINE_DMD</t>
+          <t>IND_MNRL_DMD</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -10358,187 +10358,187 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.012</t>
+          <t>0.954</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.0217152</t>
+          <t>0.910116</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.0290715494400002</t>
+          <t>0.8682506639999998</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.034011092877312</t>
+          <t>0.8283111334559998</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.7902088213170237</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.7538592155364406</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.7191816916217644</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.6860993338071631</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.6545387644520336</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.62442998128724</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.5957062021480269</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.5683037168492177</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.5421617458741537</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.5172223055639426</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.4934300795080011</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.4707322958506331</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.449078610241504</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.4284209941703947</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.4087136284385566</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.3899128015303829</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.3719768126599853</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.3548658792776259</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.3385420488308551</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.3229691145846357</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.3081125353137425</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.2939393586893103</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>1.0364927195002176</t>
+          <t>0.280418148189602</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IND_MNRL_DMD</t>
+          <t>IND_OTHR_DMD</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -10560,187 +10560,187 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.954</t>
+          <t>0.999</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.910116</t>
+          <t>0.998001</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.8682506639999998</t>
+          <t>0.997002999</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.8283111334559998</t>
+          <t>0.996005996001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0.7902088213170237</t>
+          <t>0.995009990004999</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0.7538592155364406</t>
+          <t>0.994014980014994</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.7191816916217644</t>
+          <t>0.993020965034979</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>0.6860993338071631</t>
+          <t>0.992027944069944</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0.6545387644520336</t>
+          <t>0.9910359161258742</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>0.62442998128724</t>
+          <t>0.9900448802097482</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>0.5957062021480269</t>
+          <t>0.9890548353295384</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>0.5683037168492177</t>
+          <t>0.988065780494209</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>0.5421617458741537</t>
+          <t>0.9870777147137147</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>0.5172223055639426</t>
+          <t>0.986090636999001</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>0.4934300795080011</t>
+          <t>0.985104546362002</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>0.4707322958506331</t>
+          <t>0.98411944181564</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>0.449078610241504</t>
+          <t>0.9831353223738244</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>0.4284209941703947</t>
+          <t>0.9821521870514506</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>0.4087136284385566</t>
+          <t>0.9811700348643992</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>0.3899128015303829</t>
+          <t>0.9801888648295348</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>0.3719768126599853</t>
+          <t>0.9792086759647052</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>0.3548658792776259</t>
+          <t>0.9782294672887404</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>0.3385420488308551</t>
+          <t>0.9772512378214516</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>0.3229691145846357</t>
+          <t>0.9762739865836304</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>0.3081125353137425</t>
+          <t>0.9752977125970468</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>0.2939393586893103</t>
+          <t>0.9743224148844496</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>0.280418148189602</t>
+          <t>0.9733480924695652</t>
         </is>
       </c>
     </row>
